--- a/Clone_Code_Classification.xlsx
+++ b/Clone_Code_Classification.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +481,11 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>URL_Clone_Code</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Code_Classification</t>
         </is>
       </c>
@@ -524,7 +529,12 @@
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)docetl_PR377_95e377a329106af471350cd06e2ef47c.md</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -565,7 +575,12 @@
       <c r="J3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)ailia-models_PR1704_45c599f91015cbaadc0908171f68345f.md</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -606,7 +621,12 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)inference_PR1306_d5b739fa939db6eda667ac1c4e106c98.md</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,7 +667,12 @@
       <c r="J5" t="n">
         <v>0.75</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)inference_PR1319_b68479cbb45d125c5da0d7915149c4e3.md</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -688,7 +713,12 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)inference_PR1350_63462b26e8b103e0c6db47af094813eb.md</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -729,7 +759,12 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)inference_PR1364_9cd2d8746888e5d8dbc953e4520a0998.md</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -770,7 +805,12 @@
       <c r="J8" t="n">
         <v>0.6</v>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)dagster_PR30487_a5c8c63e59128cdb74116f746692bb7c.md</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -811,7 +851,12 @@
       <c r="J9" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)dagster_PR30489_a5c8c63e59128cdb74116f746692bb7c.md</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -852,7 +897,12 @@
       <c r="J10" t="n">
         <v>0.4286</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)julep_PR1395_90950a4bb59517d726017f01b22785db.md</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -893,7 +943,12 @@
       <c r="J11" t="n">
         <v>0.5714</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)reflex-web_PR1435_bc49cb39c98356a64a31af1f652dbe33.md</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,7 +989,12 @@
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)reflex-web_PR1445_00ba1f5c2b342a82f93175d10b16a531.md</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,7 +1035,12 @@
       <c r="J13" t="n">
         <v>0.5333</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)reflex-web_PR1453_a998ce8249ef25aa4069b55e9249bced.md</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1016,7 +1081,12 @@
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)reflex-web_PR1458_7b7be769bf642aa0fa3b880639116b6f.md</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1057,7 +1127,12 @@
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)skypilot_PR6067_0fc572bac711ddb46841e11b9e8cdb11.md</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1098,7 +1173,12 @@
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)ai-shifu_PR512_538374eb009b8f8984b1b4f4d0dddc60.md</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1139,7 +1219,12 @@
       <c r="J17" t="n">
         <v>0.2727</v>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Olive_PR1897_16a3da9ced7cbe3c1773fa6d7e3ed5f9.md</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1180,7 +1265,12 @@
       <c r="J18" t="n">
         <v>0.1053</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Olive_PR1904_a64db2efc5944ee6265118bb335b1426.md</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1221,7 +1311,12 @@
       <c r="J19" t="n">
         <v>0.1053</v>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Olive_PR1907_56912c90e196b9fb4bf7e68fb92d0d95.md</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1262,7 +1357,12 @@
       <c r="J20" t="n">
         <v>0.25</v>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Olive_PR1911_ffc8a1f890b9519134100ca23e865c68.md</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1303,7 +1403,12 @@
       <c r="J21" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Olive_PR1915_ffc8a1f890b9519134100ca23e865c68.md</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1344,7 +1449,12 @@
       <c r="J22" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)docling_PR1926_7e39a7861d04d2202dbdb00e1a5153d2.md</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1385,7 +1495,12 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)marimo_PR3479_7b087e78fea0c85602636e1606dfa44d.md</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1426,7 +1541,12 @@
       <c r="J24" t="n">
         <v>0.5</v>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)marimo_PR3591_e6f355b3d5da56e5b4047dbf83edef2f.md</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1467,7 +1587,12 @@
       <c r="J25" t="n">
         <v>0.5</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)marimo_PR4008_79d74acbcfcec46dab1d1438478d7aca.md</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1508,7 +1633,12 @@
       <c r="J26" t="n">
         <v>0.2</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)marimo_PR4033_d5c9c41ee96c7be7ba6609b5613ef197.md</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1549,7 +1679,12 @@
       <c r="J27" t="n">
         <v>0.2</v>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)onnxscript_PR2388_0d2bcfe2c04126d7910c95a032f46388.md</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1590,7 +1725,12 @@
       <c r="J28" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)onnxscript_PR2401_343c7587076c82a8b270f072c4770974.md</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1631,7 +1771,12 @@
       <c r="J29" t="n">
         <v>0.2</v>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)onnxscript_PR2406_e329f24f9341551afb98d0182b8cfadb.md</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1672,7 +1817,12 @@
       <c r="J30" t="n">
         <v>0.25</v>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)onnxscript_PR2437_69ee2b8060d93a6a18695d0eb2f2cc0f.md</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1713,7 +1863,12 @@
       <c r="J31" t="n">
         <v>0.1429</v>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)onnxscript_PR2447_b10faf82266968906cab017666533a44.md</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1754,7 +1909,12 @@
       <c r="J32" t="n">
         <v>0.2</v>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)torchio_PR1330_643fdcaa3cdb098223e283f139b06180.md</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1795,7 +1955,12 @@
       <c r="J33" t="n">
         <v>0.1364</v>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)chai_PR133_7ef759b6db44d48663581ffaaea10445.md</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1836,7 +2001,12 @@
       <c r="J34" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)triton-viz_PR86_c5cecdb2a95ef6ba9987d6ddde2b797a.md</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1877,7 +2047,12 @@
       <c r="J35" t="n">
         <v>0.0357</v>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)zfit_PR644_4d509107e9408d0abbf7c59c3f40ecbe.md</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1918,7 +2093,12 @@
       <c r="J36" t="n">
         <v>0.5</v>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)lmms-eval_PR734_762a41d476c2be28e62c4a30428b1841.md</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1959,7 +2139,12 @@
       <c r="J37" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)HARK_PR1559_f0ad1bf1ff3335264a906a69a301e616.md</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2000,7 +2185,12 @@
       <c r="J38" t="n">
         <v>0.09089999999999999</v>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)litellm_PR12551_7028fd651e35123cc1bb207753bce80c.md</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2041,7 +2231,12 @@
       <c r="J39" t="n">
         <v>0.4</v>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)single-file-agents_PR8_03a0a4c49520ea8cf7f740e672bfe3df.md</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2082,7 +2277,12 @@
       <c r="J40" t="n">
         <v>0.375</v>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)single-file-agents_PR9_7415c6931cfbf7b66bde3007ac1f1cb1.md</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2123,7 +2323,12 @@
       <c r="J41" t="n">
         <v>0.5</v>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)posthog_PR35081_60185943f6dea19c55fb8f3fea5fcb0b.md</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2164,7 +2369,12 @@
       <c r="J42" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)netius_PR44_ac1bf9183c61ebdf988c32a2a8c35523.md</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2205,7 +2415,12 @@
       <c r="J43" t="n">
         <v>0.1111</v>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)btcrecover_PR609_ca925a77a542133738b0a3acde6338b6.md</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2246,7 +2461,12 @@
       <c r="J44" t="n">
         <v>0.875</v>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)btcrecover_PR611_283d78f162e36d7864172fcb9c27314d.md</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2287,7 +2507,12 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)btcrecover_PR612_1bc716c65048c6d1c59c559671c67b37.md</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2328,7 +2553,12 @@
       <c r="J46" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)chebpy_PR77_e183fbaddcf322796e79c68372b7ac76.md</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2369,7 +2599,12 @@
       <c r="J47" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)datachain_PR1191_ec682ffc0e3b9f7b3c5831eb3bfae26e.md</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2410,7 +2645,12 @@
       <c r="J48" t="n">
         <v>0.5</v>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)AutoGPT_PR9963_9b478b88805b7de4fc6b7c61147bed0c.md</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2451,7 +2691,12 @@
       <c r="J49" t="n">
         <v>0.4667</v>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)AutoGPT_PR9965_9b478b88805b7de4fc6b7c61147bed0c.md</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2492,7 +2737,12 @@
       <c r="J50" t="n">
         <v>0.0417</v>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)AutoGPT_PR10340_621fbb0ec486c1b401a28f9cbcaaca96.md</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2533,7 +2783,12 @@
       <c r="J51" t="n">
         <v>0.0357</v>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)dace_PR2019_0e663f0d3e37892ecc2cad590078d745.md</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2574,7 +2829,12 @@
       <c r="J52" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)dace_PR2077_810634abc5782ab79adc67408cd74bfd.md</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2615,7 +2875,12 @@
       <c r="J53" t="n">
         <v>0.6</v>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)cartography_PR1622_6e4475684b16c3500465799c2cdbe5c2.md</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2656,7 +2921,12 @@
       <c r="J54" t="n">
         <v>0.8889</v>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)cartography_PR1623_8352263dd83f500145a359f3378d5189.md</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2697,7 +2967,12 @@
       <c r="J55" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)cartography_PR1664_6cdcd50cff380e8f52e6698daf964dd1.md</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2738,7 +3013,12 @@
       <c r="J56" t="n">
         <v>0.125</v>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)cartography_PR1697_6cdcd50cff380e8f52e6698daf964dd1.md</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2779,7 +3059,12 @@
       <c r="J57" t="n">
         <v>0.5</v>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)onnx_PR7109_696025d5dbcf82d3051986166a76dc33.md</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2820,7 +3105,12 @@
       <c r="J58" t="n">
         <v>0.4706</v>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)onnx_PR7112_b318f37f7de4cd90c0b9b891c757b92d.md</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2861,7 +3151,12 @@
       <c r="J59" t="n">
         <v>0.1053</v>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)agentops_PR729_02db30931e107d7c74177d4d4c43fceb.md</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2902,7 +3197,12 @@
       <c r="J60" t="n">
         <v>0.5</v>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)agentops_PR1080_7f09fd6a6908230c8291291a1472e261.md</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2943,7 +3243,12 @@
       <c r="J61" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)agentops_PR1134_a9252aafb9623b120da8b450f1e8c94e.md</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2984,7 +3289,12 @@
       <c r="J62" t="n">
         <v>0.4545</v>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)fides_PR6310_8f9c52eb0334f429dde0e4255ea0b837.md</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3025,7 +3335,12 @@
       <c r="J63" t="n">
         <v>0.2308</v>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)serena_PR264_767f53688e3936ebb2baac11a6158f06.md</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3066,7 +3381,12 @@
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)fastmcp_PR1190_50dcc1f5b6451803a3ba149a8cdb5ce1.md</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3107,7 +3427,12 @@
       <c r="J65" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)kura_PR53_95264668ce6fdd5f8a87c7d99873b89c.md</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3148,7 +3473,12 @@
       <c r="J66" t="n">
         <v>0.4545</v>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Kiln_PR352_1366427e3617425d9639f0d4049e103e.md</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3189,7 +3519,12 @@
       <c r="J67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Kiln_PR355_2549e99d4cccb0a007193263538c27fd.md</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3230,7 +3565,12 @@
       <c r="J68" t="n">
         <v>0.0833</v>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Kiln_PR358_028dd53157d7cf814575a3a1c9441c99.md</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3271,7 +3611,12 @@
       <c r="J69" t="n">
         <v>0.037</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR498_f9eaedcdfed66c37a72bf9f18fbead47.md</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3312,7 +3657,12 @@
       <c r="J70" t="n">
         <v>0.2</v>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR499_7fcb9fbd99302def8272db7f613de81a.md</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3353,7 +3703,12 @@
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR501_653f6527d7b3340eaeeefb4451e71750.md</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3394,7 +3749,12 @@
       <c r="J72" t="n">
         <v>0.25</v>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR505_829b784df66f71e723e7e6f208edae6c.md</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3435,7 +3795,12 @@
       <c r="J73" t="n">
         <v>0.1111</v>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR514_accfa3c243a932c35df34b0203be08e4.md</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3476,7 +3841,12 @@
       <c r="J74" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR521_31872561115f865f5280919c3e575840.md</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3517,7 +3887,12 @@
       <c r="J75" t="n">
         <v>0.2308</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR528_efda6aa283b0f1cbadf76a49c46f3a6f.md</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3558,7 +3933,12 @@
       <c r="J76" t="n">
         <v>0.0833</v>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR536_2316ff697b5eb3782a674969fd994bc8.md</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3599,7 +3979,12 @@
       <c r="J77" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)DDNS_PR537_f6b343dd3f611d936d66920a6adbf66d.md</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3640,7 +4025,12 @@
       <c r="J78" t="n">
         <v>0.5</v>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)flynt_PR220_cd81c1590e0b93e6a70a0dda05b91c36.md</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3681,7 +4071,12 @@
       <c r="J79" t="n">
         <v>0.5</v>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)flynt_PR226_7cf49da3eb6e71fc0218391367a96768.md</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3722,7 +4117,12 @@
       <c r="J80" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)flynt_PR227_7cf49da3eb6e71fc0218391367a96768.md</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3763,7 +4163,12 @@
       <c r="J81" t="n">
         <v>0.5</v>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)flynt_PR228_7cf49da3eb6e71fc0218391367a96768.md</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3804,7 +4209,12 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)flynt_PR229_7cf49da3eb6e71fc0218391367a96768.md</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3845,7 +4255,12 @@
       <c r="J83" t="n">
         <v>1</v>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)flynt_PR239_c915a933209c8b80cbdb1b98f99566ea.md</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3886,7 +4301,12 @@
       <c r="J84" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)meta-agent_PR72_a73edf4648199fc8599cb4918fcc319b.md</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3927,7 +4347,12 @@
       <c r="J85" t="n">
         <v>1</v>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)meta-agent_PR119_21ff3b8f4317bfd2e49ded2cc2f0c779.md</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3968,7 +4393,12 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)meta-agent_PR140_8c7803138db2e91e531200387f40ce92.md</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4009,7 +4439,12 @@
       <c r="J87" t="n">
         <v>0.4286</v>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)issue-metrics_PR540_5fbaed961fc690653b208f25afb6e66f.md</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4050,7 +4485,12 @@
       <c r="J88" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)vllm_PR21146_2ba4d4bbbb10b10ef1eee1ed2623cc5d.md</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4091,7 +4531,12 @@
       <c r="J89" t="n">
         <v>0.125</v>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)debug-gym_PR126_66b04388001bce4bddbef876632b1fd9.md</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4132,7 +4577,12 @@
       <c r="J90" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)debug-gym_PR129_66b04388001bce4bddbef876632b1fd9.md</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4173,7 +4623,12 @@
       <c r="J91" t="n">
         <v>0.5</v>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)debug-gym_PR161_1a9c575a0fbd6068ae35aa804eb1d1b0.md</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4214,7 +4669,12 @@
       <c r="J92" t="n">
         <v>0.8</v>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)debug-gym_PR179_dc7a2609a4d4ad45974941175934638b.md</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4255,7 +4715,12 @@
       <c r="J93" t="n">
         <v>0.6667</v>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)haliax_PR153_b82e24a2f76c6c65faf8e76d82f4b651.md</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4296,7 +4761,12 @@
       <c r="J94" t="n">
         <v>0.0769</v>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)keep_PR5002_b6a4e475b1d4666f9f6fbbd0fc84ce8d.md</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4337,7 +4807,12 @@
       <c r="J95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)keep_PR5015_a046d760d4606ecc32186b98b8a1dca8.md</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4378,7 +4853,12 @@
       <c r="J96" t="n">
         <v>0.25</v>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)keep_PR5074_04420c2453e034f7bf13445ddde58d1e.md</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4419,7 +4899,12 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)keep_PR5101_4ca8ebeff47829f8515ea4fdf8068086.md</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4460,7 +4945,12 @@
       <c r="J98" t="n">
         <v>0.4</v>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)keep_PR5113_c137f0c109c942638025081030e94ec5.md</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4501,7 +4991,12 @@
       <c r="J99" t="n">
         <v>0.8889</v>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)weave_PR4555_8afd84e00c4e47ff0a69c9ad5bf1bcdf.md</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4542,7 +5037,12 @@
       <c r="J100" t="n">
         <v>0.4286</v>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)Qcodes_PR7240_f79bbf98f13697b7dcb349cf793266db.md</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4583,7 +5083,12 @@
       <c r="J101" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)numbagg_PR384_d03e8f175fa9aecc5dd1f18d20b44dbd.md</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4624,7 +5129,12 @@
       <c r="J102" t="n">
         <v>0.5</v>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)pylabrobot_PR549_daaa359386769f0cf4cc2b49a4795190.md</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4665,7 +5175,12 @@
       <c r="J103" t="n">
         <v>0.8</v>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)pylabrobot_PR551_bfdd060abf652811758f1e30f9ac9d15.md</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4706,7 +5221,12 @@
       <c r="J104" t="n">
         <v>0.1429</v>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)autogen_PR6690_2e203c079b076d86824e7c547532b149.md</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4747,7 +5267,12 @@
       <c r="J105" t="n">
         <v>0.2857</v>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)azure-kusto-python_PR583_5b5ecc19fe37c0dc53ee8dd2906e4d3c.md</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4788,7 +5313,12 @@
       <c r="J106" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)stride-gpt_PR72_24c21666498cadeb97887936eccaaf60.md</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4829,7 +5359,12 @@
       <c r="J107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)green-metrics-tool_PR1253_43e124e334ecf8e218ad021f6e5be916.md</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4870,7 +5405,12 @@
       <c r="J108" t="n">
         <v>0.2308</v>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)mlflow_PR15839_0dbfe38d46c2a3dcf5feee9ca6e2b496.md</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4911,7 +5451,12 @@
       <c r="J109" t="n">
         <v>0.5</v>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)mlflow_PR15856_eb4d29888a05d5446a1faffb4300d4e8.md</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4952,7 +5497,12 @@
       <c r="J110" t="n">
         <v>0.25</v>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)mlflow_PR16093_251e8e39a7f704e86cf5ae141ab3b82c.md</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4993,7 +5543,12 @@
       <c r="J111" t="n">
         <v>1</v>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)mlflow_PR16442_c0a0506385f8a3aac580c9803c1542c1.md</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5034,7 +5589,12 @@
       <c r="J112" t="n">
         <v>0.6364</v>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)mlflow_PR16878_1700d1520827c615e2bf44175d1cf263.md</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5075,7 +5635,12 @@
       <c r="J113" t="n">
         <v>1</v>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)mlflow_PR16909_d11aad00b09e35867d309c9b75d4510b.md</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5116,7 +5681,12 @@
       <c r="J114" t="n">
         <v>0.2</v>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)MoviePilot_PR4566_5fd9a3fcb9ddf9d8494d05e74eb941dc.md</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5157,7 +5727,12 @@
       <c r="J115" t="n">
         <v>1</v>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)truss_PR1679_437919697e4c4672c0ffac548b07b844.md</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5198,7 +5773,12 @@
       <c r="J116" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)cachier_PR279_b3f1b39f78de68bb6334bb823892b856.md</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5239,7 +5819,12 @@
       <c r="J117" t="n">
         <v>1</v>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)cachier_PR294_bb2d6e42cba68ca90d178a1c9eb45d81.md</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5280,7 +5865,12 @@
       <c r="J118" t="n">
         <v>0.2414</v>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)label-studio-ml-backend_PR782_c17a3184871f5743b8b014beb7587f55.md</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5321,7 +5911,12 @@
       <c r="J119" t="n">
         <v>1</v>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)sentry-python_PR4459_24f51927281189ab397e9f0ee48a5862.md</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5362,7 +5957,12 @@
       <c r="J120" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)graphrag_PR1944_8c754d4d59465abed946a339490adf49.md</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5403,7 +6003,12 @@
       <c r="J121" t="n">
         <v>0.1111</v>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)graphrag_PR1956_1aeef52993f2506a9ea5327eb08155b9.md</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5444,7 +6049,12 @@
       <c r="J122" t="n">
         <v>0.0588</v>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR1818_761458a4299f030cf34dd83a693fb1b0.md</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5485,7 +6095,12 @@
       <c r="J123" t="n">
         <v>0.8571</v>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR1828_1e7a7e3abed473e744343cbc1f5a3474.md</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5526,7 +6141,12 @@
       <c r="J124" t="n">
         <v>0.9474</v>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR1892_761458a4299f030cf34dd83a693fb1b0.md</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5567,7 +6187,12 @@
       <c r="J125" t="n">
         <v>0.0476</v>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2277_4f684f3ab7dc2bc717ae93eb663c51ec.md</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5608,7 +6233,12 @@
       <c r="J126" t="n">
         <v>0.5</v>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2396_c366425525e277e2a085f94399234383.md</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5649,7 +6279,12 @@
       <c r="J127" t="n">
         <v>0.5</v>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2548_761458a4299f030cf34dd83a693fb1b0.md</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5690,7 +6325,12 @@
       <c r="J128" t="n">
         <v>0.1538</v>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2552_1a44339c428de990d52a1ba062a98145.md</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5731,7 +6371,12 @@
       <c r="J129" t="n">
         <v>0.5</v>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2588_1a44339c428de990d52a1ba062a98145.md</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5772,7 +6417,12 @@
       <c r="J130" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2594_1a44339c428de990d52a1ba062a98145.md</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5813,7 +6463,12 @@
       <c r="J131" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2865_49b22c1a3bf03bba5040d537deecc14e.md</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5854,7 +6509,12 @@
       <c r="J132" t="n">
         <v>0.4444</v>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2866_0759c1ff5096a2a3958c8764f1ae0eba.md</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5895,7 +6555,12 @@
       <c r="J133" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2870_9a90fff51b72f8773c308c9a641228cb.md</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5936,7 +6601,12 @@
       <c r="J134" t="n">
         <v>0.1667</v>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR2946_c88c69f2e5dd5c8a3d3cbd5f7c96a31a.md</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5977,7 +6647,12 @@
       <c r="J135" t="n">
         <v>0.3077</v>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)crewAI_PR3060_805ae4a1818e2323302ff8a38f6e0883.md</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6018,7 +6693,12 @@
       <c r="J136" t="n">
         <v>0.25</v>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)graphserver_PR29_b1a890df47456339194921c8fe131bf3.md</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6059,7 +6739,12 @@
       <c r="J137" t="n">
         <v>0.2</v>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)graphserver_PR31_898f88b540585454e806a2061ec0d350.md</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6100,7 +6785,12 @@
       <c r="J138" t="n">
         <v>0.3333</v>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)graphserver_PR33_2347946931fa277dcac5939c955d1b84.md</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6141,7 +6831,12 @@
       <c r="J139" t="n">
         <v>0.1818</v>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>[https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/](https://github.com/ItaloVicente/Extract_discussion_AiDev/blob/main/extracted_clones_md/)graphserver_PR40_4c6d5d69278fab67c5716d22d846bc92.md</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
